--- a/APLOS/CostingBOQReport.xlsx
+++ b/APLOS/CostingBOQReport.xlsx
@@ -76,10 +76,10 @@
     <t>BalanceGRNQty</t>
   </si>
   <si>
-    <t>Ranchi</t>
-  </si>
-  <si>
-    <t>Plot No 615, on Ranchi Tata Road Vill- Panch, Thana-Bundu, Ranchi Jharkhand</t>
+    <t>SFWL (Garmenting)</t>
+  </si>
+  <si>
+    <t>Mouchak (1751) Kaliakair, Gazipur</t>
   </si>
   <si>
     <t>Costing BOQ Report</t>
@@ -748,8 +748,8 @@
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.8" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" fitToHeight="0" orientation="landscape"/>
   <headerFooter scaleWithDoc="1" alignWithMargins="0" differentFirst="0" differentOddEven="0">
-    <oddFooter>&amp;L&amp;"Times New Roman"&amp;06Printed By: Mizanur Rahman
-Print Date &amp;&amp; Time: 18-Apr-2022 10:02 PM&amp;R&amp;"Times New Roman"&amp;06Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Times New Roman"&amp;06Printed By: Mizan
+Print Date &amp;&amp; Time: 19-Apr-2022 10:34 AM&amp;R&amp;"Times New Roman"&amp;06Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
   <drawing r:id="rId1"/>
   <extLst/>
